--- a/Data point Supporting files/Germany 2023/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2023/Indicators.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators by country" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -40,22 +40,25 @@
     <t xml:space="preserve">GI 2020</t>
   </si>
   <si>
+    <t xml:space="preserve">ETI 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPI 2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human right abuse scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCC</t>
+  </si>
+  <si>
     <t xml:space="preserve">KOFGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPI 2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Human right abuse scaled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biodiversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCC</t>
   </si>
   <si>
     <t xml:space="preserve">Afghanistan</t>
@@ -1131,8 +1134,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K210"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -1142,7 +1145,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="12" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1176,10 +1181,13 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>71.03864</v>
@@ -1208,10 +1216,13 @@
       <c r="J2" s="3" t="n">
         <v>7.4</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>4.3995</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>44.261765</v>
@@ -1240,10 +1251,13 @@
       <c r="J3" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.879</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>53.752253</v>
@@ -1272,10 +1286,13 @@
       <c r="J4" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>4.228</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>28.328042</v>
@@ -1304,10 +1321,13 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>2.1492</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>22.763528</v>
@@ -1336,10 +1356,13 @@
       <c r="J6" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>1.2713</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>35.814398</v>
@@ -1368,10 +1391,13 @@
       <c r="J7" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>3.8558</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>27.230219</v>
@@ -1400,10 +1426,13 @@
       <c r="J8" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>1.5639</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>34.994047</v>
@@ -1432,10 +1461,13 @@
       <c r="J9" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>1.8631</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>25.683775</v>
@@ -1464,10 +1496,13 @@
       <c r="J10" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>3.5731</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>43.89455</v>
@@ -1496,10 +1531,13 @@
       <c r="J11" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>1.8204</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>27.475332</v>
@@ -1528,10 +1566,13 @@
       <c r="J12" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K12" s="6" t="n">
+        <v>1.4202</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>17.150312</v>
@@ -1560,10 +1601,13 @@
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K13" s="6" t="n">
+        <v>1.2579</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>18.027582</v>
@@ -1592,10 +1636,13 @@
       <c r="J14" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K14" s="6" t="n">
+        <v>0.5639</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>48.594386</v>
@@ -1624,10 +1671,13 @@
       <c r="J15" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K15" s="6" t="n">
+        <v>2.047</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>34.716784</v>
@@ -1656,10 +1706,13 @@
       <c r="J16" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K16" s="6" t="n">
+        <v>1.5066</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>58.154025</v>
@@ -1688,10 +1741,13 @@
       <c r="J17" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="K17" s="6" t="n">
+        <v>3.9782</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>30.624746</v>
@@ -1720,10 +1776,13 @@
       <c r="J18" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K18" s="6" t="n">
+        <v>3.8142</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>57.995609</v>
@@ -1752,10 +1811,13 @@
       <c r="J19" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K19" s="6" t="n">
+        <v>2.5307</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>21.286937</v>
@@ -1784,10 +1846,13 @@
       <c r="J20" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K20" s="6" t="n">
+        <v>0.704</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="n">
         <v>47.688012</v>
@@ -1816,10 +1881,13 @@
       <c r="J21" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K21" s="6" t="n">
+        <v>4.062</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="n">
         <v>47.157709</v>
@@ -1848,10 +1916,13 @@
       <c r="J22" s="3" t="n">
         <v>7.1</v>
       </c>
+      <c r="K22" s="6" t="n">
+        <v>4.7542</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="n">
         <v>25.992628</v>
@@ -1880,10 +1951,13 @@
       <c r="J23" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K23" s="6" t="n">
+        <v>1.8566</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="n">
         <v>32.626421</v>
@@ -1912,10 +1986,13 @@
       <c r="J24" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K24" s="6" t="n">
+        <v>2.0361</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>67.092953</v>
@@ -1944,10 +2021,13 @@
       <c r="J25" s="3" t="n">
         <v>5.2</v>
       </c>
+      <c r="K25" s="6" t="n">
+        <v>3.7938</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="n">
         <v>51.36201</v>
@@ -1976,10 +2056,13 @@
       <c r="J26" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K26" s="6" t="n">
+        <v>1.2898</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="n">
         <v>0</v>
@@ -2008,10 +2091,13 @@
       <c r="J27" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K27" s="6" t="n">
+        <v>2.6638</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="n">
         <v>31.447499</v>
@@ -2040,10 +2126,13 @@
       <c r="J28" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K28" s="6" t="n">
+        <v>2.402</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="n">
         <v>27.948113</v>
@@ -2072,10 +2161,13 @@
       <c r="J29" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K29" s="6" t="n">
+        <v>2.2839</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="n">
         <v>41.980905</v>
@@ -2104,10 +2196,13 @@
       <c r="J30" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K30" s="6" t="n">
+        <v>0.7691</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="n">
         <v>54.787588</v>
@@ -2136,10 +2231,13 @@
       <c r="J31" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K31" s="6" t="n">
+        <v>3.9989</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="n">
         <v>62.499324</v>
@@ -2168,10 +2266,13 @@
       <c r="J32" s="3" t="n">
         <v>6.2</v>
       </c>
+      <c r="K32" s="6" t="n">
+        <v>4.6073</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="n">
         <v>57.119451</v>
@@ -2200,10 +2301,13 @@
       <c r="J33" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K33" s="6" t="n">
+        <v>3.2356</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="n">
         <v>59.524752</v>
@@ -2232,10 +2336,13 @@
       <c r="J34" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K34" s="6" t="n">
+        <v>4.0267</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="n">
         <v>14.446342</v>
@@ -2264,10 +2371,13 @@
       <c r="J35" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K35" s="6" t="n">
+        <v>0.8999</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="n">
         <v>35.825757</v>
@@ -2296,10 +2406,13 @@
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K36" s="6" t="n">
+        <v>3.9532</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="n">
         <v>27.613273</v>
@@ -2328,10 +2441,13 @@
       <c r="J37" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K37" s="6" t="n">
+        <v>1.304</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="n">
         <v>68.457114</v>
@@ -2360,10 +2476,13 @@
       <c r="J38" s="3" t="n">
         <v>8.7</v>
       </c>
+      <c r="K38" s="6" t="n">
+        <v>5.104</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="n">
         <v>65.245667</v>
@@ -2392,10 +2511,13 @@
       <c r="J39" s="3" t="n">
         <v>8.6</v>
       </c>
+      <c r="K39" s="6" t="n">
+        <v>5.2786</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="n">
         <v>36.513344</v>
@@ -2424,10 +2546,13 @@
       <c r="J40" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K40" s="6" t="n">
+        <v>1.4943</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="n">
         <v>77.824398</v>
@@ -2456,10 +2581,13 @@
       <c r="J41" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K41" s="6" t="n">
+        <v>2.4449</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>74.922463</v>
@@ -2488,10 +2616,13 @@
       <c r="J42" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K42" s="6" t="n">
+        <v>2.9778</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>63.467957</v>
@@ -2520,10 +2651,13 @@
       <c r="J43" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K43" s="6" t="n">
+        <v>3.4919</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>33.776715</v>
@@ -2552,10 +2686,13 @@
       <c r="J44" s="3" t="n">
         <v>2.2</v>
       </c>
+      <c r="K44" s="6" t="n">
+        <v>1.9091</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>35.870816</v>
@@ -2584,10 +2721,13 @@
       <c r="J45" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K45" s="6" t="n">
+        <v>0.5449</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>51.426639</v>
@@ -2616,10 +2756,13 @@
       <c r="J46" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K46" s="6" t="n">
+        <v>4.1529</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>30.760428</v>
@@ -2648,10 +2791,13 @@
       <c r="J47" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K47" s="6" t="n">
+        <v>0.6425</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="n">
         <v>24.325761</v>
@@ -2680,10 +2826,13 @@
       <c r="J48" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K48" s="6" t="n">
+        <v>0.64</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B49" s="5" t="n">
         <v>67.241748</v>
@@ -2712,10 +2861,13 @@
       <c r="J49" s="3" t="n">
         <v>8.1</v>
       </c>
+      <c r="K49" s="6" t="n">
+        <v>4.3124</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50" s="5" t="n">
         <v>8.307903</v>
@@ -2744,10 +2896,13 @@
       <c r="J50" s="3" t="n">
         <v>0.8</v>
       </c>
+      <c r="K50" s="6" t="n">
+        <v>0.6792</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="5" t="n">
         <v>56.932635</v>
@@ -2776,10 +2931,13 @@
       <c r="J51" s="3" t="n">
         <v>6.3</v>
       </c>
+      <c r="K51" s="6" t="n">
+        <v>5.1959</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B52" s="5" t="n">
         <v>36.865937</v>
@@ -2808,10 +2966,13 @@
       <c r="J52" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K52" s="6" t="n">
+        <v>2.4416</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B53" s="5" t="n">
         <v>45.594002</v>
@@ -2840,10 +3001,13 @@
       <c r="J53" s="3" t="n">
         <v>4.2</v>
       </c>
+      <c r="K53" s="6" t="n">
+        <v>2.6989</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B54" s="5" t="n">
         <v>65.465487</v>
@@ -2872,10 +3036,13 @@
       <c r="J54" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K54" s="6" t="n">
+        <v>3.6722</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55" s="5" t="n">
         <v>52.46189</v>
@@ -2904,10 +3071,13 @@
       <c r="J55" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K55" s="6" t="n">
+        <v>3.3039</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B56" s="5" t="n">
         <v>50.45434</v>
@@ -2936,10 +3106,13 @@
       <c r="J56" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K56" s="6" t="n">
+        <v>2.5423</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B57" s="5" t="n">
         <v>66.06238</v>
@@ -2968,10 +3141,13 @@
       <c r="J57" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K57" s="6" t="n">
+        <v>4.2125</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B58" s="5" t="n">
         <v>71.03997</v>
@@ -3000,10 +3176,13 @@
       <c r="J58" s="3" t="n">
         <v>7.8</v>
       </c>
+      <c r="K58" s="6" t="n">
+        <v>5.1383</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B59" s="5" t="n">
         <v>18.424168</v>
@@ -3032,10 +3211,13 @@
       <c r="J59" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K59" s="6" t="n">
+        <v>0.5918</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B60" s="5" t="n">
         <v>55.917345</v>
@@ -3064,10 +3246,13 @@
       <c r="J60" s="3" t="n">
         <v>6.7</v>
       </c>
+      <c r="K60" s="6" t="n">
+        <v>4.1111</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B61" s="5" t="n">
         <v>37.852187</v>
@@ -3096,10 +3281,13 @@
       <c r="J61" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K61" s="6" t="n">
+        <v>2.9754</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B62" s="5" t="n">
         <v>3.009361</v>
@@ -3128,10 +3316,13 @@
       <c r="J62" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K62" s="6" t="n">
+        <v>0.6323</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B63" s="5" t="n">
         <v>22.755214</v>
@@ -3160,10 +3351,13 @@
       <c r="J63" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="K63" s="6" t="n">
+        <v>0.5259</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B64" s="5" t="n">
         <v>24.277408</v>
@@ -3192,10 +3386,13 @@
       <c r="J64" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K64" s="6" t="n">
+        <v>1.3218</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B65" s="5" t="n">
         <v>57.38954</v>
@@ -3224,10 +3421,13 @@
       <c r="J65" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K65" s="6" t="n">
+        <v>5.0256</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B66" s="5" t="n">
         <v>50.478991</v>
@@ -3256,10 +3456,13 @@
       <c r="J66" s="3" t="n">
         <v>6.1</v>
       </c>
+      <c r="K66" s="6" t="n">
+        <v>4.6351</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B67" s="5" t="n">
         <v>33.820858</v>
@@ -3288,10 +3491,13 @@
       <c r="J67" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K67" s="6" t="n">
+        <v>1.0477</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B68" s="5" t="n">
         <v>16.546922</v>
@@ -3320,10 +3526,13 @@
       <c r="J68" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="K68" s="6" t="n">
+        <v>0.5778</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B69" s="5" t="n">
         <v>46.293145</v>
@@ -3352,10 +3561,13 @@
       <c r="J69" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K69" s="6" t="n">
+        <v>3.4054</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B70" s="5" t="n">
         <v>36.856116</v>
@@ -3384,10 +3596,13 @@
       <c r="J70" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K70" s="6" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B71" s="5" t="n">
         <v>23.227351</v>
@@ -3416,10 +3631,13 @@
       <c r="J71" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K71" s="6" t="n">
+        <v>0.956</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B72" s="5" t="n">
         <v>38.625983</v>
@@ -3448,10 +3666,13 @@
       <c r="J72" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K72" s="6" t="n">
+        <v>2.5655</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B73" s="5" t="n">
         <v>28.203982</v>
@@ -3480,10 +3701,13 @@
       <c r="J73" s="3" t="n">
         <v>2.9</v>
       </c>
+      <c r="K73" s="6" t="n">
+        <v>2.1492</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B74" s="5" t="n">
         <v>57.352993</v>
@@ -3512,10 +3736,13 @@
       <c r="J74" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K74" s="6" t="n">
+        <v>2.4663</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B75" s="5" t="n">
         <v>58.335451</v>
@@ -3544,10 +3771,13 @@
       <c r="J75" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K75" s="6" t="n">
+        <v>4.9871</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B76" s="5" t="n">
         <v>64.48011</v>
@@ -3576,10 +3806,13 @@
       <c r="J76" s="3" t="n">
         <v>7.6</v>
       </c>
+      <c r="K76" s="6" t="n">
+        <v>4.3537</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B77" s="5" t="n">
         <v>49.250975</v>
@@ -3608,10 +3841,13 @@
       <c r="J77" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K77" s="6" t="n">
+        <v>4.6464</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B78" s="5" t="n">
         <v>71.374194</v>
@@ -3640,10 +3876,13 @@
       <c r="J78" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K78" s="6" t="n">
+        <v>2.8909</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B79" s="5" t="n">
         <v>58.306722</v>
@@ -3672,10 +3911,13 @@
       <c r="J79" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K79" s="6" t="n">
+        <v>2.8096</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B80" s="5" t="n">
         <v>19.170293</v>
@@ -3704,10 +3946,13 @@
       <c r="J80" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K80" s="6" t="n">
+        <v>1.4823</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B81" s="5" t="n">
         <v>38.716807</v>
@@ -3736,10 +3981,13 @@
       <c r="J81" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K81" s="6" t="n">
+        <v>0.5816</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B82" s="5" t="n">
         <v>16.68454</v>
@@ -3768,10 +4016,13 @@
       <c r="J82" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K82" s="6" t="n">
+        <v>0.6772</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B83" s="5" t="n">
         <v>43.703403</v>
@@ -3800,10 +4051,13 @@
       <c r="J83" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K83" s="6" t="n">
+        <v>3.0079</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B84" s="5" t="n">
         <v>60.011864</v>
@@ -3832,10 +4086,13 @@
       <c r="J84" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K84" s="6" t="n">
+        <v>2.3201</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B85" s="5" t="n">
         <v>62.454336</v>
@@ -3864,10 +4121,13 @@
       <c r="J85" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K85" s="6" t="n">
+        <v>3.8351</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="n">
         <v>66.488571</v>
@@ -3896,10 +4156,13 @@
       <c r="J86" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K86" s="6" t="n">
+        <v>3.4343</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B87" s="5" t="n">
         <v>7.355872</v>
@@ -3928,10 +4191,13 @@
       <c r="J87" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K87" s="6" t="n">
+        <v>1.4067</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B88" s="5" t="n">
         <v>26.544781</v>
@@ -3960,10 +4226,13 @@
       <c r="J88" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K88" s="6" t="n">
+        <v>0.7977</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B89" s="5" t="n">
         <v>31.495047</v>
@@ -3992,10 +4261,13 @@
       <c r="J89" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K89" s="6" t="n">
+        <v>0.5576</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B90" s="5" t="n">
         <v>45.231889</v>
@@ -4024,10 +4296,13 @@
       <c r="J90" s="3" t="n">
         <v>6.4</v>
       </c>
+      <c r="K90" s="6" t="n">
+        <v>3.8986</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B91" s="5" t="n">
         <v>42.74307</v>
@@ -4056,10 +4331,13 @@
       <c r="J91" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K91" s="6" t="n">
+        <v>3.4178</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B92" s="5" t="n">
         <v>16.917541</v>
@@ -4088,10 +4366,13 @@
       <c r="J92" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="K92" s="6" t="n">
+        <v>1.8202</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B93" s="5" t="n">
         <v>39.230696</v>
@@ -4120,10 +4401,13 @@
       <c r="J93" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K93" s="6" t="n">
+        <v>1.8369</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B94" s="5" t="n">
         <v>58.183756</v>
@@ -4152,10 +4436,13 @@
       <c r="J94" s="3" t="n">
         <v>3.2</v>
       </c>
+      <c r="K94" s="6" t="n">
+        <v>2.7215</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B95" s="5" t="n">
         <v>51.161704</v>
@@ -4184,10 +4471,13 @@
       <c r="J95" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K95" s="6" t="n">
+        <v>3.5744</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B96" s="5" t="n">
         <v>42.917977</v>
@@ -4216,10 +4506,13 @@
       <c r="J96" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K96" s="6" t="n">
+        <v>3.3728</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B97" s="5" t="n">
         <v>45.5763</v>
@@ -4248,10 +4541,13 @@
       <c r="J97" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K97" s="6" t="n">
+        <v>3.1136</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B98" s="5" t="n">
         <v>39.001507</v>
@@ -4280,10 +4576,13 @@
       <c r="J98" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K98" s="6" t="n">
+        <v>1.7985</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B99" s="5" t="n">
         <v>58.78457</v>
@@ -4312,10 +4611,13 @@
       <c r="J99" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K99" s="6" t="n">
+        <v>2.2748</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B100" s="5" t="n">
         <v>57.201045</v>
@@ -4344,10 +4646,13 @@
       <c r="J100" s="3" t="n">
         <v>5.8</v>
       </c>
+      <c r="K100" s="6" t="n">
+        <v>2.426</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B101" s="5" t="n">
         <v>28.494613</v>
@@ -4376,10 +4681,13 @@
       <c r="J101" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K101" s="6" t="n">
+        <v>0.6944</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B102" s="5" t="n">
         <v>61.696643</v>
@@ -4408,10 +4716,13 @@
       <c r="J102" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K102" s="6" t="n">
+        <v>2.292</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B103" s="5" t="n">
         <v>51.83054</v>
@@ -4440,10 +4751,13 @@
       <c r="J103" s="3" t="n">
         <v>6.2</v>
       </c>
+      <c r="K103" s="6" t="n">
+        <v>2.2503</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="n">
         <v>60.146535</v>
@@ -4472,10 +4786,13 @@
       <c r="J104" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K104" s="6" t="n">
+        <v>5.0768</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B105" s="5" t="n">
         <v>70.457876</v>
@@ -4504,10 +4821,13 @@
       <c r="J105" s="3" t="n">
         <v>6.4</v>
       </c>
+      <c r="K105" s="6" t="n">
+        <v>2.4759</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B106" s="5" t="n">
         <v>14.903216</v>
@@ -4536,10 +4856,13 @@
       <c r="J106" s="3" t="n">
         <v>1.1</v>
       </c>
+      <c r="K106" s="6" t="n">
+        <v>0.7342</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B107" s="5" t="n">
         <v>24.739967</v>
@@ -4568,10 +4891,13 @@
       <c r="J107" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K107" s="6" t="n">
+        <v>0.7274</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B108" s="5" t="n">
         <v>10.636173</v>
@@ -4600,10 +4926,13 @@
       <c r="J108" s="3" t="n">
         <v>1.2</v>
       </c>
+      <c r="K108" s="6" t="n">
+        <v>0.4385</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B109" s="5" t="n">
         <v>26.744212</v>
@@ -4632,10 +4961,13 @@
       <c r="J109" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K109" s="6" t="n">
+        <v>0.8635</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B110" s="5" t="n">
         <v>58.939597</v>
@@ -4664,10 +4996,13 @@
       <c r="J110" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="K110" s="6" t="n">
+        <v>2.871</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B111" s="5" t="n">
         <v>52.585753</v>
@@ -4696,10 +5031,13 @@
       <c r="J111" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K111" s="6" t="n">
+        <v>3.2079</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B112" s="5" t="n">
         <v>34.665527</v>
@@ -4728,10 +5066,13 @@
       <c r="J112" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K112" s="6" t="n">
+        <v>1.4279</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B113" s="5" t="n">
         <v>46.291614</v>
@@ -4760,10 +5101,13 @@
       <c r="J113" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K113" s="6" t="n">
+        <v>3.0668</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B114" s="5" t="n">
         <v>58.834008</v>
@@ -4792,10 +5136,13 @@
       <c r="J114" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K114" s="6" t="n">
+        <v>4.0154</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B115" s="5" t="n">
         <v>33.03403</v>
@@ -4824,10 +5171,13 @@
       <c r="J115" s="3" t="n">
         <v>2.8</v>
       </c>
+      <c r="K115" s="6" t="n">
+        <v>0.7756</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B116" s="5" t="n">
         <v>44.325919</v>
@@ -4856,10 +5206,13 @@
       <c r="J116" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K116" s="6" t="n">
+        <v>3.7652</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B117" s="5" t="n">
         <v>30.822573</v>
@@ -4888,10 +5241,13 @@
       <c r="J117" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K117" s="6" t="n">
+        <v>1.8566</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B118" s="5" t="n">
         <v>57.192019</v>
@@ -4920,10 +5276,13 @@
       <c r="J118" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K118" s="6" t="n">
+        <v>4.2949</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B119" s="5" t="n">
         <v>31.486076</v>
@@ -4952,10 +5311,13 @@
       <c r="J119" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="K119" s="6" t="n">
+        <v>0.6641</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B120" s="5" t="n">
         <v>57.154503</v>
@@ -4984,10 +5346,13 @@
       <c r="J120" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K120" s="6" t="n">
+        <v>1.5883</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B121" s="5" t="n">
         <v>41.368481</v>
@@ -5016,10 +5381,13 @@
       <c r="J121" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K121" s="6" t="n">
+        <v>3.5755</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B122" s="5" t="n">
         <v>45.473525</v>
@@ -5048,10 +5416,13 @@
       <c r="J122" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K122" s="6" t="n">
+        <v>1.5441</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B123" s="5" t="n">
         <v>72.283201</v>
@@ -5080,10 +5451,13 @@
       <c r="J123" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K123" s="6" t="n">
+        <v>3.3921</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="5" t="n">
         <v>40.918484</v>
@@ -5112,10 +5486,13 @@
       <c r="J124" s="3" t="n">
         <v>2.7</v>
       </c>
+      <c r="K124" s="6" t="n">
+        <v>0.829</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B125" s="5" t="n">
         <v>5.642999</v>
@@ -5144,10 +5521,13 @@
       <c r="J125" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K125" s="6" t="n">
+        <v>2.1956</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B126" s="5" t="n">
         <v>58.056611</v>
@@ -5176,10 +5556,13 @@
       <c r="J126" s="3" t="n">
         <v>6.8</v>
       </c>
+      <c r="K126" s="6" t="n">
+        <v>2.3429</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B127" s="5" t="n">
         <v>67.853849</v>
@@ -5208,10 +5591,13 @@
       <c r="J127" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K127" s="6" t="n">
+        <v>3.0679</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B128" s="5" t="n">
         <v>24.17834</v>
@@ -5240,10 +5626,13 @@
       <c r="J128" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K128" s="6" t="n">
+        <v>3.1097</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B129" s="5" t="n">
         <v>42.408028</v>
@@ -5272,10 +5661,13 @@
       <c r="J129" s="3" t="n">
         <v>3.5</v>
       </c>
+      <c r="K129" s="6" t="n">
+        <v>3.334</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B130" s="5" t="n">
         <v>53.344565</v>
@@ -5304,10 +5696,13 @@
       <c r="J130" s="3" t="n">
         <v>5.7</v>
       </c>
+      <c r="K130" s="6" t="n">
+        <v>3.6787</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B131" s="5" t="n">
         <v>13.388949</v>
@@ -5336,10 +5731,13 @@
       <c r="J131" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K131" s="6" t="n">
+        <v>0.5247</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B132" s="5" t="n">
         <v>38.122461</v>
@@ -5366,10 +5764,13 @@
         <v>0.656</v>
       </c>
       <c r="J132" s="7"/>
+      <c r="K132" s="6" t="n">
+        <v>0.5259</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B133" s="5" t="n">
         <v>37.790272</v>
@@ -5398,10 +5799,13 @@
       <c r="J133" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K133" s="6" t="n">
+        <v>1.6597</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B134" s="5" t="n">
         <v>63.402142</v>
@@ -5430,10 +5834,13 @@
       <c r="J134" s="3" t="n">
         <v>6.4</v>
       </c>
+      <c r="K134" s="6" t="n">
+        <v>2.5564</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B135" s="5" t="n">
         <v>54.372346</v>
@@ -5462,10 +5869,13 @@
       <c r="J135" s="3" t="n">
         <v>7.7</v>
       </c>
+      <c r="K135" s="6" t="n">
+        <v>4.6668</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B136" s="5" t="n">
         <v>58.868486</v>
@@ -5494,10 +5904,13 @@
       <c r="J136" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K136" s="6" t="n">
+        <v>4.9546</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B137" s="5" t="n">
         <v>69.397567</v>
@@ -5526,10 +5939,13 @@
       <c r="J137" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="K137" s="6" t="n">
+        <v>4.9481</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B138" s="5" t="n">
         <v>44.867429</v>
@@ -5558,10 +5974,13 @@
       <c r="J138" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K138" s="6" t="n">
+        <v>1.8699</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B139" s="5" t="n">
         <v>12.018166</v>
@@ -5590,10 +6009,13 @@
       <c r="J139" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K139" s="6" t="n">
+        <v>0.6958</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B140" s="5" t="n">
         <v>36.788297</v>
@@ -5622,10 +6044,13 @@
       <c r="J140" s="3" t="n">
         <v>3.9</v>
       </c>
+      <c r="K140" s="6" t="n">
+        <v>1.4677</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B141" s="5" t="n">
         <v>58.035625</v>
@@ -5654,10 +6079,13 @@
       <c r="J141" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="K141" s="6" t="n">
+        <v>3.5037</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B142" s="5" t="n">
         <v>34.881554</v>
@@ -5686,10 +6114,13 @@
       <c r="J142" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K142" s="6" t="n">
+        <v>2.1439</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B143" s="5" t="n">
         <v>46.284448</v>
@@ -5718,10 +6149,13 @@
       <c r="J143" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K143" s="6" t="n">
+        <v>2.2275</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B144" s="5" t="n">
         <v>61.793427</v>
@@ -5750,10 +6184,13 @@
       <c r="J144" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K144" s="6" t="n">
+        <v>1.6463</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B145" s="5" t="n">
         <v>52.135446</v>
@@ -5782,10 +6219,13 @@
       <c r="J145" s="3" t="n">
         <v>4.8</v>
       </c>
+      <c r="K145" s="6" t="n">
+        <v>2.6634</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B146" s="5" t="n">
         <v>48.81524</v>
@@ -5814,10 +6254,13 @@
       <c r="J146" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K146" s="6" t="n">
+        <v>1.1982</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B147" s="5" t="n">
         <v>68.6998</v>
@@ -5846,10 +6289,13 @@
       <c r="J147" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K147" s="6" t="n">
+        <v>2.9296</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B148" s="5" t="n">
         <v>32.765877</v>
@@ -5878,10 +6324,13 @@
       <c r="J148" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K148" s="6" t="n">
+        <v>0.7616</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B149" s="5" t="n">
         <v>27.536932</v>
@@ -5910,10 +6359,13 @@
       <c r="J149" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="K149" s="6" t="n">
+        <v>0.5449</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B150" s="5" t="n">
         <v>38.103242</v>
@@ -5942,10 +6394,13 @@
       <c r="J150" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K150" s="6" t="n">
+        <v>1.8649</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B151" s="5" t="n">
         <v>28.693743</v>
@@ -5974,10 +6429,13 @@
       <c r="J151" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K151" s="6" t="n">
+        <v>1.2517</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B152" s="5" t="n">
         <v>63.97275</v>
@@ -6006,10 +6464,13 @@
       <c r="J152" s="3" t="n">
         <v>7.3</v>
       </c>
+      <c r="K152" s="6" t="n">
+        <v>4.3363</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B153" s="5" t="n">
         <v>32.305137</v>
@@ -6038,10 +6499,13 @@
       <c r="J153" s="3" t="n">
         <v>3.7</v>
       </c>
+      <c r="K153" s="6" t="n">
+        <v>1.8566</v>
+      </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B154" s="5" t="n">
         <v>39.290202</v>
@@ -6070,10 +6534,13 @@
       <c r="J154" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K154" s="6" t="n">
+        <v>0.6615</v>
+      </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B155" s="5" t="n">
         <v>56.045938</v>
@@ -6102,10 +6569,13 @@
       <c r="J155" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K155" s="6" t="n">
+        <v>2.17</v>
+      </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B156" s="5" t="n">
         <v>37.327439</v>
@@ -6134,10 +6604,13 @@
       <c r="J156" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K156" s="6" t="n">
+        <v>3.6401</v>
+      </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B157" s="5" t="n">
         <v>34.305534</v>
@@ -6166,10 +6639,13 @@
       <c r="J157" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K157" s="6" t="n">
+        <v>2.0189</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B158" s="5" t="n">
         <v>36.880896</v>
@@ -6198,10 +6674,13 @@
       <c r="J158" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K158" s="6" t="n">
+        <v>2.3665</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B159" s="5" t="n">
         <v>36.065155</v>
@@ -6230,10 +6709,13 @@
       <c r="J159" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K159" s="6" t="n">
+        <v>2.5133</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B160" s="5" t="n">
         <v>34.229833</v>
@@ -6262,10 +6744,13 @@
       <c r="J160" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K160" s="6" t="n">
+        <v>2.8414</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B161" s="5" t="n">
         <v>50.699957</v>
@@ -6294,10 +6779,13 @@
       <c r="J161" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K161" s="6" t="n">
+        <v>3.7206</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B162" s="5" t="n">
         <v>35.039429</v>
@@ -6326,10 +6814,13 @@
       <c r="J162" s="3" t="n">
         <v>2.5</v>
       </c>
+      <c r="K162" s="6" t="n">
+        <v>1.5461</v>
+      </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B163" s="5" t="n">
         <v>44.204295</v>
@@ -6358,10 +6849,13 @@
       <c r="J163" s="3" t="n">
         <v>5.4</v>
       </c>
+      <c r="K163" s="6" t="n">
+        <v>3.8394</v>
+      </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B164" s="5" t="n">
         <v>45.258803</v>
@@ -6390,10 +6884,13 @@
       <c r="J164" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K164" s="6" t="n">
+        <v>1.4954</v>
+      </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B165" s="5" t="n">
         <v>31.946424</v>
@@ -6422,10 +6919,13 @@
       <c r="J165" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K165" s="6" t="n">
+        <v>1.8674</v>
+      </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B166" s="5" t="n">
         <v>57.270677</v>
@@ -6454,10 +6954,13 @@
       <c r="J166" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K166" s="6" t="n">
+        <v>4.4659</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B167" s="5" t="n">
         <v>10.56755</v>
@@ -6486,10 +6989,13 @@
       <c r="J167" s="3" t="n">
         <v>0.8</v>
       </c>
+      <c r="K167" s="6" t="n">
+        <v>0.5507</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B168" s="5" t="n">
         <v>34.489715</v>
@@ -6518,10 +7024,13 @@
       <c r="J168" s="3" t="n">
         <v>4.1</v>
       </c>
+      <c r="K168" s="6" t="n">
+        <v>0.8506</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B169" s="5" t="n">
         <v>27.96184</v>
@@ -6550,10 +7059,13 @@
       <c r="J169" s="3" t="n">
         <v>2.6</v>
       </c>
+      <c r="K169" s="6" t="n">
+        <v>0.7286</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B170" s="5" t="n">
         <v>51.558939</v>
@@ -6582,10 +7094,13 @@
       <c r="J170" s="3" t="n">
         <v>5.9</v>
       </c>
+      <c r="K170" s="6" t="n">
+        <v>3.9409</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B171" s="5" t="n">
         <v>73.960224</v>
@@ -6614,10 +7129,13 @@
       <c r="J171" s="3" t="n">
         <v>7.2</v>
       </c>
+      <c r="K171" s="6" t="n">
+        <v>4.4921</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B172" s="5" t="n">
         <v>51.587309</v>
@@ -6646,10 +7164,13 @@
       <c r="J172" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K172" s="6" t="n">
+        <v>2.116</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B173" s="5" t="n">
         <v>23.967354</v>
@@ -6678,10 +7199,13 @@
       <c r="J173" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K173" s="6" t="n">
+        <v>2.0352</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B174" s="5" t="n">
         <v>77.214438</v>
@@ -6710,10 +7234,13 @@
       <c r="J174" s="3" t="n">
         <v>9.1</v>
       </c>
+      <c r="K174" s="6" t="n">
+        <v>5.105</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B175" s="5" t="n">
         <v>30.132625</v>
@@ -6742,10 +7269,13 @@
       <c r="J175" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K175" s="6" t="n">
+        <v>0.6475</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B176" s="5" t="n">
         <v>48.921805</v>
@@ -6774,10 +7304,13 @@
       <c r="J176" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K176" s="6" t="n">
+        <v>2.6628</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B177" s="5" t="n">
         <v>70.470164</v>
@@ -6806,10 +7339,13 @@
       <c r="J177" s="3" t="n">
         <v>7.6</v>
       </c>
+      <c r="K177" s="6" t="n">
+        <v>4.4022</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B178" s="5" t="n">
         <v>49.979198</v>
@@ -6838,10 +7374,13 @@
       <c r="J178" s="3" t="n">
         <v>5.1</v>
       </c>
+      <c r="K178" s="6" t="n">
+        <v>3.5121</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B179" s="5" t="n">
         <v>54.520457</v>
@@ -6870,10 +7409,13 @@
       <c r="J179" s="3" t="n">
         <v>4.9</v>
       </c>
+      <c r="K179" s="6" t="n">
+        <v>3.6908</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B180" s="5" t="n">
         <v>6.907974</v>
@@ -6902,10 +7444,13 @@
       <c r="J180" s="3" t="n">
         <v>1.3</v>
       </c>
+      <c r="K180" s="6" t="n">
+        <v>0.7933</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B181" s="5" t="n">
         <v>10.58709</v>
@@ -6934,10 +7479,13 @@
       <c r="J181" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="K181" s="6" t="n">
+        <v>0.9798</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B182" s="5" t="n">
         <v>73.276488</v>
@@ -6966,10 +7514,13 @@
       <c r="J182" s="3" t="n">
         <v>7</v>
       </c>
+      <c r="K182" s="6" t="n">
+        <v>2.9122</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B183" s="5" t="n">
         <v>20.959445</v>
@@ -6998,10 +7549,13 @@
       <c r="J183" s="3" t="n">
         <v>2.3</v>
       </c>
+      <c r="K183" s="6" t="n">
+        <v>1.0468</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B184" s="5" t="n">
         <v>59.770057</v>
@@ -7030,10 +7584,13 @@
       <c r="J184" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K184" s="6" t="n">
+        <v>2.5484</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B185" s="5" t="n">
         <v>46.525588</v>
@@ -7062,10 +7619,13 @@
       <c r="J185" s="3" t="n">
         <v>6.1</v>
       </c>
+      <c r="K185" s="6" t="n">
+        <v>4.2147</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B186" s="5" t="n">
         <v>44.052135</v>
@@ -7094,10 +7654,13 @@
       <c r="J186" s="3" t="n">
         <v>3.8</v>
       </c>
+      <c r="K186" s="6" t="n">
+        <v>2.0397</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B187" s="5" t="n">
         <v>34.270178</v>
@@ -7126,10 +7689,13 @@
       <c r="J187" s="3" t="n">
         <v>3.3</v>
       </c>
+      <c r="K187" s="6" t="n">
+        <v>5.195</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B188" s="5" t="n">
         <v>54.667753</v>
@@ -7158,10 +7724,13 @@
       <c r="J188" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K188" s="6" t="n">
+        <v>2.4993</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B189" s="5" t="n">
         <v>53.862917</v>
@@ -7190,10 +7759,13 @@
       <c r="J189" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="K189" s="6" t="n">
+        <v>4.4815</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B190" s="5" t="n">
         <v>43.464477</v>
@@ -7222,10 +7794,13 @@
       <c r="J190" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K190" s="6" t="n">
+        <v>2.9189</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B191" s="5" t="n">
         <v>45.882894</v>
@@ -7254,10 +7829,13 @@
       <c r="J191" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K191" s="6" t="n">
+        <v>3.2218</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B192" s="5" t="n">
         <v>47.840308</v>
@@ -7286,10 +7864,13 @@
       <c r="J192" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="K192" s="6" t="n">
+        <v>2.7163</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B193" s="5" t="n">
         <v>49.741955</v>
@@ -7318,10 +7899,13 @@
       <c r="J193" s="3" t="n">
         <v>4.4</v>
       </c>
+      <c r="K193" s="6" t="n">
+        <v>2.1001</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B194" s="5" t="n">
         <v>64.140516</v>
@@ -7350,10 +7934,13 @@
       <c r="J194" s="3" t="n">
         <v>5</v>
       </c>
+      <c r="K194" s="6" t="n">
+        <v>4.7481</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B195" s="5" t="n">
         <v>42.402473</v>
@@ -7382,10 +7969,13 @@
       <c r="J195" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="K195" s="6" t="n">
+        <v>3.4554</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B196" s="5" t="n">
         <v>54.457097</v>
@@ -7414,10 +8004,13 @@
       <c r="J196" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K196" s="6" t="n">
+        <v>4.3972</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B197" s="5" t="n">
         <v>53.391751</v>
@@ -7446,10 +8039,13 @@
       <c r="J197" s="3" t="n">
         <v>3.6</v>
       </c>
+      <c r="K197" s="6" t="n">
+        <v>1.4323</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B198" s="5" t="n">
         <v>26.923655</v>
@@ -7478,10 +8074,13 @@
       <c r="J198" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K198" s="6" t="n">
+        <v>0.8675</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B199" s="5" t="n">
         <v>20.121297</v>
@@ -7510,10 +8109,13 @@
       <c r="J199" s="3" t="n">
         <v>1.6</v>
       </c>
+      <c r="K199" s="6" t="n">
+        <v>0.8417</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B200" s="5" t="n">
         <v>25.905463</v>
@@ -7542,10 +8144,13 @@
       <c r="J200" s="3" t="n">
         <v>3.1</v>
       </c>
+      <c r="K200" s="6" t="n">
+        <v>2.4263</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B201" s="5" t="n">
         <v>8.462037</v>
@@ -7574,10 +8179,13 @@
       <c r="J201" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="K201" s="6" t="n">
+        <v>1.1686</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B202" s="5" t="n">
         <v>53.046405</v>
@@ -7606,10 +8214,13 @@
       <c r="J202" s="3" t="n">
         <v>3.4</v>
       </c>
+      <c r="K202" s="6" t="n">
+        <v>3.4617</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B203" s="5" t="n">
         <v>47.45611</v>
@@ -7638,10 +8249,13 @@
       <c r="J203" s="3" t="n">
         <v>6</v>
       </c>
+      <c r="K203" s="6" t="n">
+        <v>3.1384</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B204" s="5" t="n">
         <v>72.983545</v>
@@ -7670,10 +8284,13 @@
       <c r="J204" s="3" t="n">
         <v>6.9</v>
       </c>
+      <c r="K204" s="6" t="n">
+        <v>4.4085</v>
+      </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B205" s="5" t="n">
         <v>47.829047</v>
@@ -7702,10 +8319,13 @@
       <c r="J205" s="3" t="n">
         <v>4.3</v>
       </c>
+      <c r="K205" s="6" t="n">
+        <v>2.6906</v>
+      </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B206" s="5" t="n">
         <v>34.820275</v>
@@ -7734,10 +8354,13 @@
       <c r="J206" s="3" t="n">
         <v>4.7</v>
       </c>
+      <c r="K206" s="6" t="n">
+        <v>1.2713</v>
+      </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B207" s="5" t="n">
         <v>55.324939</v>
@@ -7766,10 +8389,13 @@
       <c r="J207" s="3" t="n">
         <v>5.6</v>
       </c>
+      <c r="K207" s="6" t="n">
+        <v>3.0773</v>
+      </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B208" s="5" t="n">
         <v>72.381046</v>
@@ -7798,10 +8424,13 @@
       <c r="J208" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="K208" s="6" t="n">
+        <v>2.3167</v>
+      </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B209" s="5" t="n">
         <v>34.714513</v>
@@ -7830,10 +8459,13 @@
       <c r="J209" s="3" t="n">
         <v>6.6</v>
       </c>
+      <c r="K209" s="6" t="n">
+        <v>2.603</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B210" s="5" t="n">
         <v>62.856889</v>
@@ -7861,6 +8493,9 @@
       </c>
       <c r="J210" s="3" t="n">
         <v>5.9</v>
+      </c>
+      <c r="K210" s="6" t="n">
+        <v>3.7432</v>
       </c>
     </row>
   </sheetData>
@@ -7880,7 +8515,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -7891,27 +8526,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>17.8</v>
@@ -7931,7 +8566,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>25</v>
@@ -7951,7 +8586,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>18.7</v>
@@ -7971,7 +8606,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>20.2</v>
@@ -7991,7 +8626,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>15.9</v>
@@ -8011,7 +8646,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>39</v>
@@ -8031,7 +8666,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>26.8</v>
@@ -8051,7 +8686,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>17.2</v>
@@ -8071,7 +8706,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>50.9</v>
@@ -8091,7 +8726,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>10</v>
@@ -8111,7 +8746,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>10.5</v>
@@ -8131,7 +8766,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>28.3</v>
@@ -8151,7 +8786,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>35.7</v>
@@ -8171,7 +8806,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>16.7</v>
@@ -8191,7 +8826,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>14.3</v>
@@ -8211,7 +8846,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>33.3</v>
@@ -8231,7 +8866,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>41.8</v>
@@ -8251,7 +8886,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>42.3</v>
@@ -8271,7 +8906,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>25.9</v>
@@ -8291,7 +8926,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>54.5</v>
@@ -8311,7 +8946,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>29.6</v>
@@ -8331,7 +8966,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>22.3</v>
@@ -8351,7 +8986,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>44.5</v>
@@ -8371,7 +9006,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>20.6</v>
@@ -8391,7 +9026,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>22.3</v>
@@ -8411,7 +9046,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>19.9</v>
@@ -8431,7 +9066,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>23.9</v>
@@ -8451,7 +9086,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>30</v>
@@ -8471,7 +9106,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>21.1</v>
@@ -8491,7 +9126,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>10.4</v>
@@ -8511,7 +9146,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>11.6</v>
@@ -8531,7 +9166,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>26.2</v>
@@ -8551,7 +9186,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>36.9</v>
@@ -8571,7 +9206,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>22.4</v>
@@ -8591,7 +9226,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>10.4</v>
@@ -8626,22 +9261,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -8649,7 +9284,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.33</v>
@@ -8657,7 +9292,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0.67</v>
@@ -8665,7 +9300,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -8688,28 +9323,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0</v>
@@ -8717,10 +9352,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.33</v>
@@ -8728,10 +9363,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>1</v>
@@ -8739,10 +9374,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
@@ -8750,10 +9385,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -8761,10 +9396,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -8772,10 +9407,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0.67</v>
@@ -8783,10 +9418,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0.33</v>
@@ -8794,10 +9429,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
@@ -8805,10 +9440,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -8816,10 +9451,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -8827,10 +9462,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0.67</v>
@@ -8838,10 +9473,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0</v>
@@ -8849,10 +9484,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0.33</v>
@@ -8860,10 +9495,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -8871,10 +9506,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -8882,10 +9517,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>0.33</v>
@@ -8893,10 +9528,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -8904,10 +9539,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>0</v>
@@ -8915,10 +9550,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -8926,10 +9561,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0.33</v>
@@ -8937,10 +9572,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>0.33</v>
@@ -8948,10 +9583,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0.67</v>
@@ -8959,10 +9594,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0</v>
@@ -8970,10 +9605,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C26" s="1" t="n">
         <v>0.33</v>
@@ -8981,10 +9616,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C27" s="1" t="n">
         <v>0.67</v>
@@ -8992,10 +9627,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C28" s="1" t="n">
         <v>1</v>
@@ -9003,10 +9638,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>0.67</v>
@@ -9014,10 +9649,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>0</v>
@@ -9025,10 +9660,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>0.33</v>
@@ -9036,10 +9671,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="1" t="n">
         <v>0</v>
@@ -9047,10 +9682,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C33" s="1" t="n">
         <v>0</v>
@@ -9058,10 +9693,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C34" s="1" t="n">
         <v>0</v>
@@ -9069,10 +9704,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C35" s="1" t="n">
         <v>1</v>
@@ -9080,10 +9715,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C36" s="1" t="n">
         <v>0.33</v>
@@ -9091,10 +9726,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C37" s="1" t="n">
         <v>1</v>
@@ -9117,235 +9752,235 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="BU1" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>0</v>
@@ -9566,7 +10201,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>0.45</v>
@@ -9787,7 +10422,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>0</v>
@@ -10008,7 +10643,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0</v>
@@ -10229,7 +10864,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>0</v>
@@ -10450,7 +11085,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>0</v>
@@ -10668,7 +11303,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0</v>
@@ -10889,7 +11524,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0</v>
@@ -11110,7 +11745,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0</v>
@@ -11325,7 +11960,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.25</v>
@@ -11546,7 +12181,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>0</v>
@@ -11767,7 +12402,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>0</v>
@@ -11988,7 +12623,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B14" s="1" t="n">
         <v>0</v>
@@ -12209,7 +12844,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="n">
         <v>0</v>
@@ -12430,7 +13065,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B16" s="1" t="n">
         <v>0</v>
@@ -12651,7 +13286,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0</v>
@@ -12872,7 +13507,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B18" s="1" t="n">
         <v>0</v>
@@ -13093,7 +13728,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="n">
         <v>0</v>
@@ -13314,7 +13949,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="1" t="n">
         <v>0</v>
@@ -13535,7 +14170,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>0</v>
@@ -13756,7 +14391,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>0</v>
@@ -13977,7 +14612,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>0</v>
@@ -14198,7 +14833,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>0</v>
@@ -14419,7 +15054,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>0</v>
@@ -14640,7 +15275,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" s="1" t="n">
         <v>0</v>
@@ -14861,7 +15496,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="1" t="n">
         <v>0</v>
@@ -15082,7 +15717,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" s="1" t="n">
         <v>0</v>
@@ -15300,7 +15935,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>0</v>
@@ -15521,7 +16156,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" s="1" t="n">
         <v>0</v>
@@ -15742,7 +16377,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B31" s="1" t="n">
         <v>0</v>
@@ -15963,7 +16598,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B32" s="1" t="n">
         <v>0</v>
@@ -16184,7 +16819,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B33" s="1" t="n">
         <v>0</v>
@@ -16405,7 +17040,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>0</v>
@@ -16626,7 +17261,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B35" s="1" t="n">
         <v>0.11</v>
@@ -16844,7 +17479,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B36" s="1" t="n">
         <v>0</v>
@@ -17080,31 +17715,31 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B2" s="9" t="n">
         <v>5657</v>
@@ -17121,7 +17756,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>760</v>
@@ -17138,7 +17773,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>845</v>
@@ -17155,7 +17790,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B5" s="9" t="n">
         <v>1111</v>
@@ -17172,7 +17807,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="9" t="n">
         <v>1000</v>
@@ -17189,7 +17824,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>740</v>
@@ -17206,7 +17841,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>1065</v>
@@ -17223,7 +17858,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>1685</v>
@@ -17240,7 +17875,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>51</v>
@@ -17257,7 +17892,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>2742</v>
@@ -17274,7 +17909,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>280</v>
@@ -17291,7 +17926,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>107</v>
@@ -17308,7 +17943,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B14" s="9" t="n">
         <v>1526</v>
@@ -17325,7 +17960,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>707</v>
@@ -17342,7 +17977,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>196</v>
@@ -17359,7 +17994,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>7925</v>
@@ -17376,7 +18011,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B18" s="9" t="n">
         <v>2899</v>
@@ -17393,7 +18028,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>848</v>
@@ -17410,7 +18045,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B20" s="9" t="n">
         <v>1941</v>
@@ -17427,7 +18062,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>545</v>
@@ -17444,7 +18079,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B22" s="9" t="n">
         <v>2128</v>
@@ -17461,7 +18096,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>1491</v>
@@ -17478,7 +18113,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B24" s="9" t="n">
         <v>1475</v>
@@ -17495,7 +18130,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>37724</v>
@@ -17527,25 +18162,25 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.23828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="n">
@@ -17554,7 +18189,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="n">
@@ -17563,7 +18198,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="n">
@@ -17572,7 +18207,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="n">
@@ -17581,10 +18216,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>50</v>
@@ -17592,7 +18227,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="n">
@@ -17601,10 +18236,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.05</v>
@@ -17612,10 +18247,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
@@ -17623,10 +18258,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>75</v>
@@ -17634,10 +18269,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>

--- a/Data point Supporting files/Germany 2023/Indicators.xlsx
+++ b/Data point Supporting files/Germany 2023/Indicators.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Indicators by country" sheetId="1" state="visible" r:id="rId2"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="322">
   <si>
     <t xml:space="preserve">Country</t>
   </si>
@@ -989,6 +989,9 @@
   </si>
   <si>
     <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disaster coping capacity</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1079,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1102,10 +1105,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1135,7 +1134,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K210"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
@@ -5763,7 +5762,9 @@
       <c r="I132" s="1" t="n">
         <v>0.656</v>
       </c>
-      <c r="J132" s="7"/>
+      <c r="J132" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K132" s="6" t="n">
         <v>0.5259</v>
       </c>
@@ -8515,7 +8516,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.33"/>
@@ -8768,7 +8769,7 @@
       <c r="A13" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="7" t="n">
         <v>28.3</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -9261,7 +9262,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -9323,7 +9324,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -9752,7 +9753,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BU36"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="1" style="0" width="10.67"/>
   </cols>
@@ -17715,7 +17716,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -17741,16 +17742,16 @@
       <c r="A2" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>5657</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="8" t="n">
         <v>735884</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="8" t="n">
         <v>223164117</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="8" t="n">
         <v>44871596</v>
       </c>
     </row>
@@ -17761,13 +17762,13 @@
       <c r="B3" s="2" t="n">
         <v>760</v>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="8" t="n">
         <v>96638</v>
       </c>
-      <c r="D3" s="9" t="n">
+      <c r="D3" s="8" t="n">
         <v>51851714</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="8" t="n">
         <v>21746387</v>
       </c>
     </row>
@@ -17778,13 +17779,13 @@
       <c r="B4" s="2" t="n">
         <v>845</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="8" t="n">
         <v>84489</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>20513232</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>6237679</v>
       </c>
     </row>
@@ -17792,16 +17793,16 @@
       <c r="A5" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>1111</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>91820</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26450736</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>6672014</v>
       </c>
     </row>
@@ -17809,16 +17810,16 @@
       <c r="A6" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>94291</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>19386814</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>6074119</v>
       </c>
     </row>
@@ -17829,13 +17830,13 @@
       <c r="B7" s="2" t="n">
         <v>740</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>127089</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>46406184</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>11401632</v>
       </c>
     </row>
@@ -17843,16 +17844,16 @@
       <c r="A8" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>1065</v>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>86015</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>13416303</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>4669973</v>
       </c>
     </row>
@@ -17860,16 +17861,16 @@
       <c r="A9" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>1685</v>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>494976</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>246358650</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>60636600</v>
       </c>
     </row>
@@ -17880,13 +17881,13 @@
       <c r="B10" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>19973</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>96802275</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>33247186</v>
       </c>
     </row>
@@ -17894,16 +17895,16 @@
       <c r="A11" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="8" t="n">
         <v>2742</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>321503</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>75660612</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>24363310</v>
       </c>
     </row>
@@ -17914,13 +17915,13 @@
       <c r="B12" s="2" t="n">
         <v>280</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>69015</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>21109914</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>6764847</v>
       </c>
     </row>
@@ -17931,13 +17932,13 @@
       <c r="B13" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>13581</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>3094227</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>901620</v>
       </c>
     </row>
@@ -17945,16 +17946,16 @@
       <c r="A14" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>1526</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>199891</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>55818328</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>18399429</v>
       </c>
     </row>
@@ -17965,13 +17966,13 @@
       <c r="B15" s="2" t="n">
         <v>707</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>177992</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>79967867</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>14078179</v>
       </c>
     </row>
@@ -17982,13 +17983,13 @@
       <c r="B16" s="2" t="n">
         <v>196</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="8" t="n">
         <v>60163</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>61150207</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>7897356</v>
       </c>
     </row>
@@ -17996,16 +17997,16 @@
       <c r="A17" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B17" s="8" t="n">
         <v>7925</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="8" t="n">
         <v>684224</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>145260386</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>52566737</v>
       </c>
     </row>
@@ -18013,16 +18014,16 @@
       <c r="A18" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>2899</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="8" t="n">
         <v>672777</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>208851717</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>67741958</v>
       </c>
     </row>
@@ -18033,13 +18034,13 @@
       <c r="B19" s="2" t="n">
         <v>848</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <v>152452</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>46175590</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>14759704</v>
       </c>
     </row>
@@ -18047,16 +18048,16 @@
       <c r="A20" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>1941</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="8" t="n">
         <v>277207</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>76084854</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>25240308</v>
       </c>
     </row>
@@ -18067,13 +18068,13 @@
       <c r="B21" s="2" t="n">
         <v>545</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <v>97144</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>35623072</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>16151379</v>
       </c>
     </row>
@@ -18081,16 +18082,16 @@
       <c r="A22" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>2128</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="8" t="n">
         <v>489246</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>151391095</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>48654726</v>
       </c>
     </row>
@@ -18098,16 +18099,16 @@
       <c r="A23" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B23" s="8" t="n">
         <v>1491</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="8" t="n">
         <v>271635</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>73072764</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>30200481</v>
       </c>
     </row>
@@ -18115,16 +18116,16 @@
       <c r="A24" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="8" t="n">
         <v>1475</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="8" t="n">
         <v>989570</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>697691493</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>129152263</v>
       </c>
     </row>
@@ -18132,16 +18133,16 @@
       <c r="A25" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B25" s="8" t="n">
         <v>37724</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="8" t="n">
         <v>6307575</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>2475302151</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>652429483</v>
       </c>
     </row>
@@ -18161,8 +18162,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="11.2421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultColWidth="11.2578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="10.67"/>
   </cols>
@@ -18276,6 +18277,14 @@
       </c>
       <c r="C11" s="4" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
